--- a/AAII_Financials/Yearly/HD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HD_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>HD</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45319</v>
+      </c>
+      <c r="E7" s="2">
         <v>44955</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44591</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43499</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43128</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42764</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42400</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42036</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41672</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41308</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40937</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>152669000</v>
+      </c>
+      <c r="E8" s="3">
         <v>157403000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>151157000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>132110000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>110225000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>108203000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>100904000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>94595000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>88519000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>83176000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>78812000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>74754000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>70395000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>101709000</v>
+      </c>
+      <c r="E9" s="3">
         <v>104625000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>100325000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>87257000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>72653000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71043000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>66548000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62282000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>58254000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>54787000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>51897000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>48912000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>46133000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>50960000</v>
+      </c>
+      <c r="E10" s="3">
         <v>52778000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50832000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44853000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>37572000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37160000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>34356000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32313000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30265000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28389000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26915000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25842000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24262000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,29 +961,32 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>262000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>247000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -981,57 +1000,63 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2673000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2455000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2386000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2128000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1989000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1870000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1811000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1754000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1690000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1640000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1627000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1568000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1573000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>130980000</v>
+      </c>
+      <c r="E17" s="3">
         <v>133364000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128117000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>113832000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>94382000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>92673000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>86223000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>81168000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>76745000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>72707000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>69646000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>66988000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63734000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21689000</v>
+      </c>
+      <c r="E18" s="3">
         <v>24039000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>23040000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18278000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15843000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15530000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14681000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13427000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11774000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10469000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9166000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7766000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6661000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E20" s="3">
         <v>55000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>44000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>47000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>73000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>77000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>74000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>36000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>166000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>337000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>87000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>13000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25114000</v>
+      </c>
+      <c r="E21" s="3">
         <v>27069000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>25946000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20844000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>18212000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17759000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16817000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15436000</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>10935000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9537000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8356000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1943000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1617000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1347000</v>
       </c>
       <c r="F22" s="3">
         <v>1347000</v>
       </c>
       <c r="G22" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="H22" s="3">
         <v>1201000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1051000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1057000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>972000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>919000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>830000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>711000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>632000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>606000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19924000</v>
+      </c>
+      <c r="E23" s="3">
         <v>22477000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21737000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16978000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14715000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14556000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13698000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12491000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11021000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9976000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8467000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7221000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6068000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4781000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5372000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5304000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4112000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3473000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3520000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4941000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4534000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4012000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3631000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3082000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2686000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2185000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15143000</v>
+      </c>
+      <c r="E26" s="3">
         <v>17105000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16433000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12866000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11242000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11036000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8757000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7957000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7009000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6345000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5385000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4535000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3883000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15143000</v>
+      </c>
+      <c r="E27" s="3">
         <v>17105000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16433000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12866000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11242000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11036000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8757000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7957000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7009000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6345000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5385000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4535000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3883000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1539,17 +1599,17 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>85000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-127000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1563,12 +1623,15 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-55000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-44000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-47000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-73000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-77000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-74000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-36000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-166000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-337000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-87000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-13000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15143000</v>
+      </c>
+      <c r="E33" s="3">
         <v>17105000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16433000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12866000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11242000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11121000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8630000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7957000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7009000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6345000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5385000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4535000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3883000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15143000</v>
+      </c>
+      <c r="E35" s="3">
         <v>17105000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16433000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12866000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11242000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11121000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8630000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7957000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7009000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6345000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5385000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4535000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3883000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45319</v>
+      </c>
+      <c r="E38" s="2">
         <v>44955</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44591</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43499</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43128</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42764</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42400</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42036</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41672</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41308</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40937</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3760000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2757000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2343000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7895000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2133000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1778000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3595000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2538000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>2216000</v>
       </c>
       <c r="L41" s="3">
         <v>2216000</v>
       </c>
       <c r="M41" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="N41" s="3">
         <v>1929000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2494000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1987000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1985,177 +2074,192 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3328000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3317000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3426000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2992000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2106000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1936000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1952000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2029000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1890000</v>
       </c>
       <c r="L43" s="3">
         <v>1890000</v>
       </c>
       <c r="M43" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="N43" s="3">
         <v>1398000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1395000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1245000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20976000</v>
+      </c>
+      <c r="E44" s="3">
         <v>24886000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>22068000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16627000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14531000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13925000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12748000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12549000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>11809000</v>
       </c>
       <c r="L44" s="3">
         <v>11809000</v>
       </c>
       <c r="M44" s="3">
+        <v>11809000</v>
+      </c>
+      <c r="N44" s="3">
         <v>11057000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10710000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10325000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1711000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1511000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1218000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>963000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1040000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>890000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>638000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>608000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1647000</v>
       </c>
       <c r="L45" s="3">
         <v>1647000</v>
       </c>
       <c r="M45" s="3">
+        <v>1647000</v>
+      </c>
+      <c r="N45" s="3">
         <v>895000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>773000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>963000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29775000</v>
+      </c>
+      <c r="E46" s="3">
         <v>32471000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29055000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28477000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19810000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18529000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18933000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17724000</v>
-      </c>
-      <c r="K46" s="3">
-        <v>16484000</v>
       </c>
       <c r="L46" s="3">
         <v>16484000</v>
       </c>
       <c r="M46" s="3">
+        <v>16484000</v>
+      </c>
+      <c r="N46" s="3">
         <v>15279000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15372000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14520000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2190,98 +2294,107 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>140000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>135000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34038000</v>
+      </c>
+      <c r="E48" s="3">
         <v>32572000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31167000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30667000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28365000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22375000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22075000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21914000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>61457000</v>
       </c>
       <c r="L48" s="3">
         <v>61457000</v>
       </c>
       <c r="M48" s="3">
+        <v>61457000</v>
+      </c>
+      <c r="N48" s="3">
         <v>23348000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24069000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24448000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12061000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10767000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10952000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7126000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2254000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2252000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2275000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2093000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>2102000</v>
       </c>
       <c r="L49" s="3">
         <v>2102000</v>
       </c>
       <c r="M49" s="3">
+        <v>2102000</v>
+      </c>
+      <c r="N49" s="3">
         <v>1289000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1170000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1120000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>656000</v>
+      </c>
+      <c r="E52" s="3">
         <v>635000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>702000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4311000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>807000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>847000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1246000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1235000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>2459000</v>
       </c>
       <c r="L52" s="3">
         <v>2459000</v>
       </c>
       <c r="M52" s="3">
+        <v>2459000</v>
+      </c>
+      <c r="N52" s="3">
         <v>602000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>333000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>295000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76530000</v>
+      </c>
+      <c r="E54" s="3">
         <v>76445000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71876000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>70581000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>51236000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44003000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44529000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42966000</v>
-      </c>
-      <c r="K54" s="3">
-        <v>41973000</v>
       </c>
       <c r="L54" s="3">
         <v>41973000</v>
       </c>
       <c r="M54" s="3">
+        <v>41973000</v>
+      </c>
+      <c r="N54" s="3">
         <v>40518000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41084000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40518000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10037000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11443000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13462000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11606000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7787000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7755000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7244000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7000000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>6565000</v>
       </c>
       <c r="L57" s="3">
         <v>6565000</v>
       </c>
       <c r="M57" s="3">
+        <v>6565000</v>
+      </c>
+      <c r="N57" s="3">
         <v>5797000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5376000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4856000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1368000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1231000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3482000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1416000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2813000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2395000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2761000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1252000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>427000</v>
       </c>
       <c r="L58" s="3">
         <v>427000</v>
       </c>
       <c r="M58" s="3">
+        <v>427000</v>
+      </c>
+      <c r="N58" s="3">
         <v>33000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1321000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>30000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10610000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10436000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11749000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10144000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7775000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6566000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6189000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5881000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>7475000</v>
       </c>
       <c r="L59" s="3">
         <v>7475000</v>
       </c>
       <c r="M59" s="3">
+        <v>7475000</v>
+      </c>
+      <c r="N59" s="3">
         <v>4919000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4765000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4490000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22015000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23110000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28693000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23166000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18375000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16716000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16194000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14133000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>12524000</v>
       </c>
       <c r="L60" s="3">
         <v>12524000</v>
       </c>
       <c r="M60" s="3">
+        <v>12524000</v>
+      </c>
+      <c r="N60" s="3">
         <v>10749000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11462000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9376000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42743000</v>
+      </c>
+      <c r="E61" s="3">
         <v>41962000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36604000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35822000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28670000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26807000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24267000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22349000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>20789000</v>
       </c>
       <c r="L61" s="3">
         <v>20789000</v>
       </c>
       <c r="M61" s="3">
+        <v>20789000</v>
+      </c>
+      <c r="N61" s="3">
         <v>14691000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9475000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10758000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10728000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9811000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8275000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8294000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7307000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2358000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2614000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2151000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>2344000</v>
       </c>
       <c r="L62" s="3">
         <v>2344000</v>
       </c>
       <c r="M62" s="3">
+        <v>2344000</v>
+      </c>
+      <c r="N62" s="3">
         <v>2556000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2370000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2486000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>75486000</v>
+      </c>
+      <c r="E66" s="3">
         <v>74883000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>73572000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>67282000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54352000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45881000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43075000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38633000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>35657000</v>
       </c>
       <c r="L66" s="3">
         <v>35657000</v>
       </c>
       <c r="M66" s="3">
+        <v>35657000</v>
+      </c>
+      <c r="N66" s="3">
         <v>27996000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23307000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22620000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>83656000</v>
+      </c>
+      <c r="E72" s="3">
         <v>76896000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>67580000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58134000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>51729000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>46423000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39935000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>35519000</v>
-      </c>
-      <c r="K72" s="3">
-        <v>30973000</v>
       </c>
       <c r="L72" s="3">
         <v>30973000</v>
       </c>
       <c r="M72" s="3">
+        <v>30973000</v>
+      </c>
+      <c r="N72" s="3">
         <v>23180000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20038000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17246000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1044000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1562000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1696000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3299000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-3116000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1878000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1454000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4333000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>6316000</v>
       </c>
       <c r="L76" s="3">
         <v>6316000</v>
       </c>
       <c r="M76" s="3">
+        <v>6316000</v>
+      </c>
+      <c r="N76" s="3">
         <v>12522000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17777000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17898000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45319</v>
+      </c>
+      <c r="E80" s="2">
         <v>44955</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44591</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43499</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43128</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42764</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42400</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42036</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41672</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41308</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40937</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15143000</v>
+      </c>
+      <c r="E81" s="3">
         <v>17105000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16433000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12866000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11242000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11121000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8630000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7957000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7009000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6345000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5385000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4535000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3883000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3247000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2975000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2862000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2519000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2296000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2152000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2062000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1973000</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>1757000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1684000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1682000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21172000</v>
+      </c>
+      <c r="E89" s="3">
         <v>14615000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16571000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18839000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13687000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13165000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12031000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9783000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>8242000</v>
       </c>
       <c r="L89" s="3">
         <v>8242000</v>
       </c>
       <c r="M89" s="3">
+        <v>8242000</v>
+      </c>
+      <c r="N89" s="3">
         <v>7628000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6975000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6651000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3226000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3119000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2566000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2463000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2678000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2442000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1897000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1621000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1442000</v>
       </c>
       <c r="L91" s="3">
         <v>-1442000</v>
       </c>
       <c r="M91" s="3">
+        <v>-1442000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1389000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1312000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1221000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4729000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3140000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2969000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10170000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2653000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2416000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2228000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1583000</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-1507000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1432000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1129000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-8383000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-7789000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-6985000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-6451000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-5958000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-4704000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-4212000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3404000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-2530000</v>
       </c>
       <c r="L96" s="3">
         <v>-2530000</v>
       </c>
       <c r="M96" s="3">
+        <v>-2530000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2243000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1743000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1632000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15443000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10993000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19120000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2983000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10798000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12547000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8870000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7870000</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>-6652000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5034000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4048000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-68000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-34000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>76000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>119000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-19000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>124000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8000</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>-34000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-32000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1003000</v>
+      </c>
+      <c r="E102" s="3">
         <v>414000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5552000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5762000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>355000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1817000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1057000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>322000</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-206000</v>
       </c>
       <c r="L102" s="3">
         <v>-206000</v>
       </c>
       <c r="M102" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="N102" s="3">
         <v>-565000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>507000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1442000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>HD</t>
   </si>
@@ -976,14 +976,14 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>262000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>247000</v>
@@ -1092,7 +1092,7 @@
         <v>94382000</v>
       </c>
       <c r="I17" s="3">
-        <v>92673000</v>
+        <v>92426000</v>
       </c>
       <c r="J17" s="3">
         <v>86223000</v>
@@ -1137,7 +1137,7 @@
         <v>15843000</v>
       </c>
       <c r="I18" s="3">
-        <v>15530000</v>
+        <v>15777000</v>
       </c>
       <c r="J18" s="3">
         <v>14681000</v>
@@ -1185,26 +1185,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>178000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>55000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>44000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>47000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>73000</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="3">
-        <v>77000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>74000</v>
+        <v>16000</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>36000</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>25114000</v>
+        <v>24362000</v>
       </c>
       <c r="E21" s="3">
-        <v>27069000</v>
+        <v>26494000</v>
       </c>
       <c r="F21" s="3">
-        <v>25946000</v>
+        <v>25426000</v>
       </c>
       <c r="G21" s="3">
-        <v>20844000</v>
+        <v>20406000</v>
       </c>
       <c r="H21" s="3">
-        <v>18212000</v>
+        <v>17832000</v>
       </c>
       <c r="I21" s="3">
-        <v>17759000</v>
+        <v>17631000</v>
       </c>
       <c r="J21" s="3">
-        <v>16817000</v>
+        <v>16492000</v>
       </c>
       <c r="K21" s="3">
         <v>15436000</v>
@@ -1381,10 +1381,10 @@
         <v>3473000</v>
       </c>
       <c r="I24" s="3">
-        <v>3520000</v>
+        <v>3435000</v>
       </c>
       <c r="J24" s="3">
-        <v>4941000</v>
+        <v>5068000</v>
       </c>
       <c r="K24" s="3">
         <v>4534000</v>
@@ -1471,10 +1471,10 @@
         <v>11242000</v>
       </c>
       <c r="I26" s="3">
-        <v>11036000</v>
+        <v>11121000</v>
       </c>
       <c r="J26" s="3">
-        <v>8757000</v>
+        <v>8630000</v>
       </c>
       <c r="K26" s="3">
         <v>7957000</v>
@@ -1516,10 +1516,10 @@
         <v>11242000</v>
       </c>
       <c r="I27" s="3">
-        <v>11036000</v>
+        <v>11121000</v>
       </c>
       <c r="J27" s="3">
-        <v>8757000</v>
+        <v>8630000</v>
       </c>
       <c r="K27" s="3">
         <v>7957000</v>
@@ -1590,26 +1590,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-127000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,26 +1725,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-178000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-55000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-47000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-73000</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I32" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-74000</v>
+        <v>-16000</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>-36000</v>
@@ -2263,26 +2263,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>120000</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2363,7 +2363,7 @@
         <v>10952000</v>
       </c>
       <c r="G49" s="3">
-        <v>7126000</v>
+        <v>10738000</v>
       </c>
       <c r="H49" s="3">
         <v>2254000</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>656000</v>
+        <v>343000</v>
       </c>
       <c r="E52" s="3">
-        <v>635000</v>
+        <v>316000</v>
       </c>
       <c r="F52" s="3">
-        <v>702000</v>
+        <v>300000</v>
       </c>
       <c r="G52" s="3">
-        <v>4311000</v>
+        <v>222000</v>
       </c>
       <c r="H52" s="3">
-        <v>807000</v>
+        <v>548000</v>
       </c>
       <c r="I52" s="3">
-        <v>847000</v>
+        <v>726000</v>
       </c>
       <c r="J52" s="3">
-        <v>1246000</v>
+        <v>1127000</v>
       </c>
       <c r="K52" s="3">
         <v>1235000</v>
@@ -2707,19 +2707,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1368000</v>
+        <v>2418000</v>
       </c>
       <c r="E58" s="3">
-        <v>1231000</v>
+        <v>2176000</v>
       </c>
       <c r="F58" s="3">
-        <v>3482000</v>
+        <v>4312000</v>
       </c>
       <c r="G58" s="3">
-        <v>1416000</v>
+        <v>2244000</v>
       </c>
       <c r="H58" s="3">
-        <v>2813000</v>
+        <v>3641000</v>
       </c>
       <c r="I58" s="3">
         <v>2395000</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10610000</v>
+        <v>2790000</v>
       </c>
       <c r="E59" s="3">
-        <v>10436000</v>
+        <v>3114000</v>
       </c>
       <c r="F59" s="3">
-        <v>11749000</v>
+        <v>3754000</v>
       </c>
       <c r="G59" s="3">
-        <v>10144000</v>
+        <v>3016000</v>
       </c>
       <c r="H59" s="3">
-        <v>7775000</v>
+        <v>2171000</v>
       </c>
       <c r="I59" s="3">
-        <v>6566000</v>
+        <v>1793000</v>
       </c>
       <c r="J59" s="3">
-        <v>6189000</v>
+        <v>1859000</v>
       </c>
       <c r="K59" s="3">
         <v>5881000</v>
@@ -2842,19 +2842,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>42743000</v>
+        <v>50683000</v>
       </c>
       <c r="E61" s="3">
-        <v>41962000</v>
+        <v>48966000</v>
       </c>
       <c r="F61" s="3">
-        <v>36604000</v>
+        <v>41957000</v>
       </c>
       <c r="G61" s="3">
-        <v>35822000</v>
+        <v>41178000</v>
       </c>
       <c r="H61" s="3">
-        <v>28670000</v>
+        <v>33736000</v>
       </c>
       <c r="I61" s="3">
         <v>26807000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10728000</v>
+        <v>1925000</v>
       </c>
       <c r="E62" s="3">
-        <v>9811000</v>
+        <v>1788000</v>
       </c>
       <c r="F62" s="3">
-        <v>8275000</v>
+        <v>2013000</v>
       </c>
       <c r="G62" s="3">
-        <v>8294000</v>
+        <v>1807000</v>
       </c>
       <c r="H62" s="3">
-        <v>7307000</v>
+        <v>1535000</v>
       </c>
       <c r="I62" s="3">
-        <v>2358000</v>
+        <v>1867000</v>
       </c>
       <c r="J62" s="3">
-        <v>2614000</v>
+        <v>2174000</v>
       </c>
       <c r="K62" s="3">
         <v>2151000</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8383000</v>
+        <v>8383000</v>
       </c>
       <c r="E96" s="3">
-        <v>-7789000</v>
+        <v>7789000</v>
       </c>
       <c r="F96" s="3">
-        <v>-6985000</v>
+        <v>6985000</v>
       </c>
       <c r="G96" s="3">
-        <v>-6451000</v>
+        <v>6451000</v>
       </c>
       <c r="H96" s="3">
-        <v>-5958000</v>
+        <v>5958000</v>
       </c>
       <c r="I96" s="3">
-        <v>-4704000</v>
+        <v>4704000</v>
       </c>
       <c r="J96" s="3">
-        <v>-4212000</v>
+        <v>4212000</v>
       </c>
       <c r="K96" s="3">
         <v>-3404000</v>

--- a/AAII_Financials/Yearly/HD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>HD</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E7" s="2">
         <v>45319</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44955</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44591</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43863</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43499</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43128</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42764</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42400</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42036</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41672</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41308</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40937</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>159514000</v>
+      </c>
+      <c r="E8" s="3">
         <v>152669000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>157403000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>151157000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>132110000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>110225000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>108203000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>100904000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>94595000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>88519000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>83176000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>78812000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74754000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70395000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>106206000</v>
+      </c>
+      <c r="E9" s="3">
         <v>101709000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>104625000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>100325000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>87257000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>72653000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71043000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>66548000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>62282000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>58254000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>54787000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>51897000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>48912000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>46133000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>53308000</v>
+      </c>
+      <c r="E10" s="3">
         <v>50960000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52778000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>50832000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>44853000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37572000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>37160000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34356000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32313000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30265000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28389000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26915000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25842000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24262000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,9 +980,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -985,12 +1004,12 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>247000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1003,60 +1022,66 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3034000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2673000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2455000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2386000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2128000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1989000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1870000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1811000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1754000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1690000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1640000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1627000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1568000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1573000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>137988000</v>
+      </c>
+      <c r="E17" s="3">
         <v>130980000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>133364000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>128117000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>113832000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>94382000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>92426000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>86223000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81168000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>76745000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>72707000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>69646000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>66988000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>63734000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21526000</v>
+      </c>
+      <c r="E18" s="3">
         <v>21689000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24039000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>23040000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18278000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15843000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15777000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14681000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13427000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11774000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10469000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9166000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7766000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6661000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,8 +1212,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1200,213 +1233,228 @@
       <c r="H20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>16000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>36000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>166000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>337000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>87000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>24560000</v>
+      </c>
+      <c r="E21" s="3">
         <v>24362000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26494000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25426000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20406000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17832000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17631000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16492000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15436000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>10935000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9537000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8356000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2321000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1943000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1617000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1347000</v>
       </c>
       <c r="G22" s="3">
         <v>1347000</v>
       </c>
       <c r="H22" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="I22" s="3">
         <v>1201000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1051000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1057000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>972000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>919000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>830000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>711000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>632000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>606000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19406000</v>
+      </c>
+      <c r="E23" s="3">
         <v>19924000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22477000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21737000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16978000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14715000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14556000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13698000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12491000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11021000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9976000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8467000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7221000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6068000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4600000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4781000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5372000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5304000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4112000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3473000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3435000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5068000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4534000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4012000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3631000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3082000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2686000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2185000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14806000</v>
+      </c>
+      <c r="E26" s="3">
         <v>15143000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17105000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16433000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12866000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11242000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11121000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8630000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7957000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7009000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6345000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5385000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4535000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3883000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14806000</v>
+      </c>
+      <c r="E27" s="3">
         <v>15143000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17105000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16433000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12866000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11242000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11121000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8630000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7957000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7009000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6345000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5385000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4535000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3883000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1626,12 +1686,15 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,9 +1785,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1740,78 +1809,84 @@
       <c r="H32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>-16000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-36000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-166000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-337000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-87000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14806000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15143000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17105000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16433000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12866000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11242000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11121000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8630000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7957000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7009000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6345000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5385000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4535000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3883000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14806000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15143000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17105000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16433000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12866000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11242000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11121000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8630000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7957000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7009000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6345000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5385000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4535000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3883000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E38" s="2">
         <v>45319</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44955</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44591</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43863</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43499</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43128</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42764</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42400</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42036</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41672</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41308</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40937</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3760000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2757000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2343000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7895000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2133000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1778000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3595000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2538000</v>
-      </c>
-      <c r="L41" s="3">
-        <v>2216000</v>
       </c>
       <c r="M41" s="3">
         <v>2216000</v>
       </c>
       <c r="N41" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="O41" s="3">
         <v>1929000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2494000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1987000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2077,189 +2166,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4903000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3328000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3317000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3426000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2992000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2106000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1936000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1952000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2029000</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1890000</v>
       </c>
       <c r="M43" s="3">
         <v>1890000</v>
       </c>
       <c r="N43" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="O43" s="3">
         <v>1398000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1395000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1245000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23451000</v>
+      </c>
+      <c r="E44" s="3">
         <v>20976000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24886000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>22068000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16627000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14531000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13925000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12748000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12549000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>11809000</v>
       </c>
       <c r="M44" s="3">
         <v>11809000</v>
       </c>
       <c r="N44" s="3">
+        <v>11809000</v>
+      </c>
+      <c r="O44" s="3">
         <v>11057000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10710000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10325000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1711000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1511000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1218000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>963000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1040000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>890000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>638000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>608000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1647000</v>
       </c>
       <c r="M45" s="3">
         <v>1647000</v>
       </c>
       <c r="N45" s="3">
+        <v>1647000</v>
+      </c>
+      <c r="O45" s="3">
         <v>895000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>773000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>963000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31683000</v>
+      </c>
+      <c r="E46" s="3">
         <v>29775000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32471000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29055000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28477000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19810000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18529000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18933000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17724000</v>
-      </c>
-      <c r="L46" s="3">
-        <v>16484000</v>
       </c>
       <c r="M46" s="3">
         <v>16484000</v>
       </c>
       <c r="N46" s="3">
+        <v>16484000</v>
+      </c>
+      <c r="O46" s="3">
         <v>15279000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15372000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14520000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2269,23 +2373,23 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>58000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>172000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>120000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2297,104 +2401,113 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>140000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>135000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35294000</v>
+      </c>
+      <c r="E48" s="3">
         <v>34038000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32572000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31167000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30667000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28365000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22375000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22075000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21914000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>61457000</v>
       </c>
       <c r="M48" s="3">
         <v>61457000</v>
       </c>
       <c r="N48" s="3">
+        <v>61457000</v>
+      </c>
+      <c r="O48" s="3">
         <v>23348000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24069000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24448000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28458000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12061000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10767000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10952000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10738000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2254000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2252000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2275000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2093000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>2102000</v>
       </c>
       <c r="M49" s="3">
         <v>2102000</v>
       </c>
       <c r="N49" s="3">
+        <v>2102000</v>
+      </c>
+      <c r="O49" s="3">
         <v>1289000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1170000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1120000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>684000</v>
+      </c>
+      <c r="E52" s="3">
         <v>343000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>316000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>222000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>548000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>726000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1127000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1235000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>2459000</v>
       </c>
       <c r="M52" s="3">
         <v>2459000</v>
       </c>
       <c r="N52" s="3">
+        <v>2459000</v>
+      </c>
+      <c r="O52" s="3">
         <v>602000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>333000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>295000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>96119000</v>
+      </c>
+      <c r="E54" s="3">
         <v>76530000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76445000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71876000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>70581000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>51236000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44003000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44529000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42966000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>41973000</v>
       </c>
       <c r="M54" s="3">
         <v>41973000</v>
       </c>
       <c r="N54" s="3">
+        <v>41973000</v>
+      </c>
+      <c r="O54" s="3">
         <v>40518000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41084000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40518000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11938000</v>
+      </c>
+      <c r="E57" s="3">
         <v>10037000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11443000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13462000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11606000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7787000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7755000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7244000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7000000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>6565000</v>
       </c>
       <c r="M57" s="3">
         <v>6565000</v>
       </c>
       <c r="N57" s="3">
+        <v>6565000</v>
+      </c>
+      <c r="O57" s="3">
         <v>5797000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5376000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4856000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6172000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2418000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2176000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4312000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2244000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3641000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2395000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2761000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1252000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>427000</v>
       </c>
       <c r="M58" s="3">
         <v>427000</v>
       </c>
       <c r="N58" s="3">
+        <v>427000</v>
+      </c>
+      <c r="O58" s="3">
         <v>33000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1321000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>30000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8236000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2790000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3114000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3754000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3016000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2171000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1793000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1859000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5881000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>7475000</v>
       </c>
       <c r="M59" s="3">
         <v>7475000</v>
       </c>
       <c r="N59" s="3">
+        <v>7475000</v>
+      </c>
+      <c r="O59" s="3">
         <v>4919000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4765000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4490000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28661000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22015000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23110000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28693000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23166000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18375000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16716000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16194000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14133000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>12524000</v>
       </c>
       <c r="M60" s="3">
         <v>12524000</v>
       </c>
       <c r="N60" s="3">
+        <v>12524000</v>
+      </c>
+      <c r="O60" s="3">
         <v>10749000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11462000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9376000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56118000</v>
+      </c>
+      <c r="E61" s="3">
         <v>50683000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48966000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41957000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41178000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33736000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26807000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24267000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22349000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>20789000</v>
       </c>
       <c r="M61" s="3">
         <v>20789000</v>
       </c>
       <c r="N61" s="3">
+        <v>20789000</v>
+      </c>
+      <c r="O61" s="3">
         <v>14691000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9475000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10758000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4700000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1925000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1788000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2013000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1807000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1535000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1867000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2174000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2151000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2344000</v>
       </c>
       <c r="M62" s="3">
         <v>2344000</v>
       </c>
       <c r="N62" s="3">
+        <v>2344000</v>
+      </c>
+      <c r="O62" s="3">
         <v>2556000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2370000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2486000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>89479000</v>
+      </c>
+      <c r="E66" s="3">
         <v>75486000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74883000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>73572000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>67282000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54352000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45881000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43075000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38633000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>35657000</v>
       </c>
       <c r="M66" s="3">
         <v>35657000</v>
       </c>
       <c r="N66" s="3">
+        <v>35657000</v>
+      </c>
+      <c r="O66" s="3">
         <v>27996000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23307000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22620000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>83656000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>76896000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>67580000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58134000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>51729000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46423000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>39935000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>35519000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>30973000</v>
       </c>
       <c r="M72" s="3">
         <v>30973000</v>
       </c>
       <c r="N72" s="3">
+        <v>30973000</v>
+      </c>
+      <c r="O72" s="3">
         <v>23180000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20038000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17246000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6640000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1044000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1562000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1696000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3299000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-3116000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1878000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1454000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4333000</v>
-      </c>
-      <c r="L76" s="3">
-        <v>6316000</v>
       </c>
       <c r="M76" s="3">
         <v>6316000</v>
       </c>
       <c r="N76" s="3">
+        <v>6316000</v>
+      </c>
+      <c r="O76" s="3">
         <v>12522000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17777000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17898000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E80" s="2">
         <v>45319</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44955</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44591</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43863</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43499</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43128</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42764</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42400</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42036</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41672</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41308</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40937</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14806000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15143000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17105000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16433000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12866000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11242000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11121000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8630000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7957000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7009000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6345000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5385000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4535000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3883000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3336000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3247000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2975000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2862000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2519000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2296000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2152000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2062000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1973000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>1757000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1684000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1682000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19810000</v>
+      </c>
+      <c r="E89" s="3">
         <v>21172000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14615000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16571000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18839000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13687000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13165000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12031000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9783000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>8242000</v>
       </c>
       <c r="M89" s="3">
         <v>8242000</v>
       </c>
       <c r="N89" s="3">
+        <v>8242000</v>
+      </c>
+      <c r="O89" s="3">
         <v>7628000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6975000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6651000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3485000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3226000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3119000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2566000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2463000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2678000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2442000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1897000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1621000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1442000</v>
       </c>
       <c r="M91" s="3">
         <v>-1442000</v>
       </c>
       <c r="N91" s="3">
+        <v>-1442000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1389000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1312000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1221000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21031000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4729000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3140000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2969000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10170000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2653000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2416000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2228000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1583000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-1507000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1432000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1129000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>8929000</v>
+      </c>
+      <c r="E96" s="3">
         <v>8383000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>7789000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>6985000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>6451000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5958000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>4704000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4212000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3404000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-2530000</v>
       </c>
       <c r="M96" s="3">
         <v>-2530000</v>
       </c>
       <c r="N96" s="3">
+        <v>-2530000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-2243000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1743000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1632000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-694000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15443000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10993000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19120000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2983000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10798000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12547000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8870000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7870000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-6652000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5034000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4048000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-186000</v>
+      </c>
+      <c r="E101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-68000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-34000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>76000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>119000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-19000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>124000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>-34000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2101000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1003000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>414000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5552000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5762000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>355000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1817000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1057000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>322000</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-206000</v>
       </c>
       <c r="M102" s="3">
         <v>-206000</v>
       </c>
       <c r="N102" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="O102" s="3">
         <v>-565000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>507000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1442000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>HD</t>
   </si>
@@ -2608,7 +2608,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>684000</v>
+        <v>415000</v>
       </c>
       <c r="E52" s="3">
         <v>343000</v>
@@ -2888,7 +2888,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8236000</v>
+        <v>3442000</v>
       </c>
       <c r="E59" s="3">
         <v>2790000</v>
@@ -2984,7 +2984,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>56118000</v>
+        <v>56913000</v>
       </c>
       <c r="E61" s="3">
         <v>50683000</v>
@@ -3032,7 +3032,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4700000</v>
+        <v>1943000</v>
       </c>
       <c r="E62" s="3">
         <v>1925000</v>
@@ -3483,8 +3483,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>89533000</v>
       </c>
       <c r="E72" s="3">
         <v>83656000</v>
@@ -3896,10 +3896,10 @@
         <v>3336000</v>
       </c>
       <c r="E83" s="3">
-        <v>3247000</v>
+        <v>3061000</v>
       </c>
       <c r="F83" s="3">
-        <v>2975000</v>
+        <v>2796000</v>
       </c>
       <c r="G83" s="3">
         <v>2862000</v>

--- a/AAII_Financials/Yearly/HD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>HD</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E7" s="2">
         <v>45690</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45319</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44591</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43863</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43499</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43128</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42764</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42400</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42036</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41672</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41308</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40937</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>164683000</v>
+      </c>
+      <c r="E8" s="3">
         <v>159514000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>152669000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>157403000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>151157000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>132110000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>110225000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>108203000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100904000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>94595000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>88519000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>83176000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>78812000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>74754000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>70395000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>109818000</v>
+      </c>
+      <c r="E9" s="3">
         <v>106206000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>101709000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>104625000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>100325000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>87257000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>72653000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71043000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>66548000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>62282000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>58254000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>54787000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>51897000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>48912000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>46133000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>54865000</v>
+      </c>
+      <c r="E10" s="3">
         <v>53308000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50960000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>52778000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50832000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>44853000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>37572000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>37160000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34356000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>32313000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30265000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28389000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26915000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25842000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24262000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,9 +999,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1007,12 +1026,12 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>247000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1025,63 +1044,69 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3273000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3034000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2673000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2455000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2386000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2128000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1989000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1870000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1811000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1754000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1690000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1640000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1627000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1568000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1573000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>143793000</v>
+      </c>
+      <c r="E17" s="3">
         <v>137988000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>130980000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>133364000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>128117000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>113832000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>94382000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>92426000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>86223000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>81168000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>76745000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>72707000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>69646000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>66988000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63734000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20890000</v>
+      </c>
+      <c r="E18" s="3">
         <v>21526000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>21689000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24039000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23040000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18278000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15843000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15777000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14681000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13427000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11774000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10469000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9166000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7766000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6661000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,8 +1245,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1236,225 +1269,240 @@
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>16000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>36000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>166000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>337000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>87000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>13000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>24163000</v>
+      </c>
+      <c r="E21" s="3">
         <v>24560000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24362000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26494000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25426000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>20406000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17832000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17631000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16492000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15436000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>10935000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9537000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8356000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2412000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2321000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1943000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1617000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1347000</v>
       </c>
       <c r="H22" s="3">
         <v>1347000</v>
       </c>
       <c r="I22" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="J22" s="3">
         <v>1201000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1051000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1057000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>972000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>919000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>830000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>711000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>632000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>606000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18602000</v>
+      </c>
+      <c r="E23" s="3">
         <v>19406000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19924000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22477000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21737000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16978000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14715000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14556000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13698000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12491000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11021000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9976000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8467000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7221000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6068000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4446000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4600000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4781000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5372000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5304000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4112000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3473000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3435000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5068000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4534000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4012000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3631000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3082000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2686000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2185000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14156000</v>
+      </c>
+      <c r="E26" s="3">
         <v>14806000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15143000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17105000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16433000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12866000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11242000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11121000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8630000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7957000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7009000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6345000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5385000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4535000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3883000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14156000</v>
+      </c>
+      <c r="E27" s="3">
         <v>14806000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15143000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17105000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16433000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12866000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11242000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11121000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8630000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7957000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7009000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6345000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5385000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4535000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3883000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1689,12 +1749,15 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,9 +1854,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1812,81 +1881,87 @@
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-16000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-36000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-166000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-337000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-87000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-13000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14156000</v>
+      </c>
+      <c r="E33" s="3">
         <v>14806000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15143000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17105000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16433000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12866000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11242000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11121000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8630000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7957000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7009000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6345000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5385000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4535000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3883000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14156000</v>
+      </c>
+      <c r="E35" s="3">
         <v>14806000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15143000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17105000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16433000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12866000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11242000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11121000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8630000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7957000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7009000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6345000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5385000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4535000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3883000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E38" s="2">
         <v>45690</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45319</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44591</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43863</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43499</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43128</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42764</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42400</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42036</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41672</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41308</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40937</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1389000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1659000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3760000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2757000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2343000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7895000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2133000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1778000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3595000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2538000</v>
-      </c>
-      <c r="M41" s="3">
-        <v>2216000</v>
       </c>
       <c r="N41" s="3">
         <v>2216000</v>
       </c>
       <c r="O41" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="P41" s="3">
         <v>1929000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2494000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1987000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2169,201 +2258,216 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5597000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4903000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3328000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3317000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3426000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2992000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2106000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1936000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1952000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2029000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1890000</v>
       </c>
       <c r="N43" s="3">
         <v>1890000</v>
       </c>
       <c r="O43" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="P43" s="3">
         <v>1398000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1395000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1245000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>25817000</v>
+      </c>
+      <c r="E44" s="3">
         <v>23451000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20976000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24886000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22068000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16627000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14531000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13925000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12748000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12549000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>11809000</v>
       </c>
       <c r="N44" s="3">
         <v>11809000</v>
       </c>
       <c r="O44" s="3">
+        <v>11809000</v>
+      </c>
+      <c r="P44" s="3">
         <v>11057000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10710000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10325000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1588000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1670000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1711000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1511000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1218000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>963000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1040000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>890000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>638000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>608000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1647000</v>
       </c>
       <c r="N45" s="3">
         <v>1647000</v>
       </c>
       <c r="O45" s="3">
+        <v>1647000</v>
+      </c>
+      <c r="P45" s="3">
         <v>895000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>773000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>963000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34391000</v>
+      </c>
+      <c r="E46" s="3">
         <v>31683000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29775000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32471000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29055000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28477000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19810000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18529000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18933000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17724000</v>
-      </c>
-      <c r="M46" s="3">
-        <v>16484000</v>
       </c>
       <c r="N46" s="3">
         <v>16484000</v>
       </c>
       <c r="O46" s="3">
+        <v>16484000</v>
+      </c>
+      <c r="P46" s="3">
         <v>15279000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15372000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14520000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2376,23 +2480,23 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>58000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>172000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>120000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2404,110 +2508,119 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>140000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>135000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37225000</v>
+      </c>
+      <c r="E48" s="3">
         <v>35294000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34038000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32572000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31167000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30667000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28365000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22375000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22075000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21914000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>61457000</v>
       </c>
       <c r="N48" s="3">
         <v>61457000</v>
       </c>
       <c r="O48" s="3">
+        <v>61457000</v>
+      </c>
+      <c r="P48" s="3">
         <v>23348000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24069000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24448000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32673000</v>
+      </c>
+      <c r="E49" s="3">
         <v>28458000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12061000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10767000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10952000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10738000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2254000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2252000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2275000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2093000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2102000</v>
       </c>
       <c r="N49" s="3">
         <v>2102000</v>
       </c>
       <c r="O49" s="3">
+        <v>2102000</v>
+      </c>
+      <c r="P49" s="3">
         <v>1289000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1170000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1120000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E52" s="3">
         <v>415000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>343000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>316000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>222000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>548000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>726000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1127000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1235000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>2459000</v>
       </c>
       <c r="N52" s="3">
         <v>2459000</v>
       </c>
       <c r="O52" s="3">
+        <v>2459000</v>
+      </c>
+      <c r="P52" s="3">
         <v>602000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>333000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>295000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105095000</v>
+      </c>
+      <c r="E54" s="3">
         <v>96119000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76530000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>76445000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71876000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70581000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51236000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44003000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44529000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42966000</v>
-      </c>
-      <c r="M54" s="3">
-        <v>41973000</v>
       </c>
       <c r="N54" s="3">
         <v>41973000</v>
       </c>
       <c r="O54" s="3">
+        <v>41973000</v>
+      </c>
+      <c r="P54" s="3">
         <v>40518000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41084000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40518000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11491000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11938000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10037000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11443000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13462000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11606000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7787000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7755000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7244000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7000000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>6565000</v>
       </c>
       <c r="N57" s="3">
         <v>6565000</v>
       </c>
       <c r="O57" s="3">
+        <v>6565000</v>
+      </c>
+      <c r="P57" s="3">
         <v>5797000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5376000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4856000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10849000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6172000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2418000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2176000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4312000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2244000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3641000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2395000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2761000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1252000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>427000</v>
       </c>
       <c r="N58" s="3">
         <v>427000</v>
       </c>
       <c r="O58" s="3">
+        <v>427000</v>
+      </c>
+      <c r="P58" s="3">
         <v>33000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1321000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>30000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2689000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3442000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2790000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3114000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3754000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3016000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2171000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1793000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1859000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5881000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>7475000</v>
       </c>
       <c r="N59" s="3">
         <v>7475000</v>
       </c>
       <c r="O59" s="3">
+        <v>7475000</v>
+      </c>
+      <c r="P59" s="3">
         <v>4919000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4765000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4490000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32424000</v>
+      </c>
+      <c r="E60" s="3">
         <v>28661000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22015000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23110000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28693000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23166000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18375000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16716000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16194000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14133000</v>
-      </c>
-      <c r="M60" s="3">
-        <v>12524000</v>
       </c>
       <c r="N60" s="3">
         <v>12524000</v>
       </c>
       <c r="O60" s="3">
+        <v>12524000</v>
+      </c>
+      <c r="P60" s="3">
         <v>10749000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11462000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9376000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>55060000</v>
+      </c>
+      <c r="E61" s="3">
         <v>56913000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>50683000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>48966000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41957000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>41178000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33736000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26807000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24267000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22349000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>20789000</v>
       </c>
       <c r="N61" s="3">
         <v>20789000</v>
       </c>
       <c r="O61" s="3">
+        <v>20789000</v>
+      </c>
+      <c r="P61" s="3">
         <v>14691000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9475000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10758000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1953000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1943000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1925000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1788000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2013000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1807000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1535000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1867000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2174000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2151000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2344000</v>
       </c>
       <c r="N62" s="3">
         <v>2344000</v>
       </c>
       <c r="O62" s="3">
+        <v>2344000</v>
+      </c>
+      <c r="P62" s="3">
         <v>2556000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2370000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2486000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92282000</v>
+      </c>
+      <c r="E66" s="3">
         <v>89479000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75486000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74883000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>73572000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>67282000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54352000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45881000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43075000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38633000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>35657000</v>
       </c>
       <c r="N66" s="3">
         <v>35657000</v>
       </c>
       <c r="O66" s="3">
+        <v>35657000</v>
+      </c>
+      <c r="P66" s="3">
         <v>27996000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23307000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22620000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>94537000</v>
+      </c>
+      <c r="E72" s="3">
         <v>89533000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>83656000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>76896000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>67580000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58134000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51729000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>46423000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>39935000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>35519000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>30973000</v>
       </c>
       <c r="N72" s="3">
         <v>30973000</v>
       </c>
       <c r="O72" s="3">
+        <v>30973000</v>
+      </c>
+      <c r="P72" s="3">
         <v>23180000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20038000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17246000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12813000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6640000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1044000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1562000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1696000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3299000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-3116000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1878000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1454000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4333000</v>
-      </c>
-      <c r="M76" s="3">
-        <v>6316000</v>
       </c>
       <c r="N76" s="3">
         <v>6316000</v>
       </c>
       <c r="O76" s="3">
+        <v>6316000</v>
+      </c>
+      <c r="P76" s="3">
         <v>12522000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17777000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17898000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E80" s="2">
         <v>45690</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45319</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44591</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43863</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43499</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43128</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42764</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42400</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42036</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41672</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41308</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40937</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14156000</v>
+      </c>
+      <c r="E81" s="3">
         <v>14806000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15143000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17105000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16433000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12866000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11242000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11121000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8630000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7957000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7009000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6345000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5385000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4535000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3883000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3514000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3336000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3061000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2796000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2862000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2519000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2296000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2152000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2062000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1973000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>1757000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1684000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1682000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16325000</v>
+      </c>
+      <c r="E89" s="3">
         <v>19810000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21172000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14615000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16571000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18839000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13687000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13165000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12031000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9783000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>8242000</v>
       </c>
       <c r="N89" s="3">
         <v>8242000</v>
       </c>
       <c r="O89" s="3">
+        <v>8242000</v>
+      </c>
+      <c r="P89" s="3">
         <v>7628000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6975000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6651000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3679000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3485000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3226000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3119000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2566000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2463000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2678000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2442000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1897000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1621000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1442000</v>
       </c>
       <c r="N91" s="3">
         <v>-1442000</v>
       </c>
       <c r="O91" s="3">
+        <v>-1442000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1389000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1312000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1221000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8980000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21031000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4729000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3140000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2969000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10170000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2653000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2416000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2228000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1583000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1507000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1432000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1129000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9152000</v>
+      </c>
+      <c r="E96" s="3">
         <v>8929000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>8383000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>7789000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>6985000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>6451000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5958000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4704000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>4212000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3404000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-2530000</v>
       </c>
       <c r="N96" s="3">
         <v>-2530000</v>
       </c>
       <c r="O96" s="3">
+        <v>-2530000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2243000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1743000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1632000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7714000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-694000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15443000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10993000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-19120000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2983000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10798000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12547000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8870000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7870000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-6652000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5034000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4048000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-186000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-68000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>76000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>119000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-19000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>124000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>-34000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-32000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-270000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2101000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1003000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>414000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5552000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5762000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>355000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1817000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1057000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>322000</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-206000</v>
       </c>
       <c r="N102" s="3">
         <v>-206000</v>
       </c>
       <c r="O102" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="P102" s="3">
         <v>-565000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>507000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1442000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
